--- a/2026 NM ORACLE Arts React Internship .xlsx
+++ b/2026 NM ORACLE Arts React Internship .xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="96">
   <si>
     <t>S.No</t>
   </si>
@@ -285,9 +285,6 @@
   </si>
   <si>
     <t>astvu24724724uo9003</t>
-  </si>
-  <si>
-    <t>https://github.com/murganp565-dot/React-internship-.git</t>
   </si>
   <si>
     <t>Anandhi. D</t>
@@ -322,30 +319,24 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
-      <color theme="1"/>
+      <color/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <color/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.0"/>
-      <color theme="1"/>
+      <color/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF222222"/>
       <name val="Arial"/>
     </font>
+    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -373,32 +364,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -413,10 +389,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,21 +503,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="6350" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="12700" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln cap="flat" cmpd="sng" w="19050" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -562,7 +534,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" rotWithShape="0" algn="ctr" dir="5400000" dist="19050">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -618,16 +590,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="26.0"/>
-    <col customWidth="1" min="2" max="2" width="13.88"/>
+    <col customWidth="1" min="2" max="2" width="13.86"/>
     <col customWidth="1" min="3" max="6" width="26.0"/>
-    <col customWidth="1" min="7" max="7" width="53.25"/>
-    <col customWidth="1" min="8" max="26" width="26.0"/>
+    <col customWidth="1" min="7" max="7" width="53.29"/>
+    <col customWidth="1" min="8" max="10" width="26.0"/>
+    <col customWidth="1" min="11" max="11" width="12.57"/>
   </cols>
   <sheetData>
-    <row r="3">
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="15.75" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -656,7 +631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="B4" s="2">
         <v>1.0</v>
       </c>
@@ -682,7 +657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
@@ -695,15 +670,15 @@
       <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="5" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -715,7 +690,7 @@
       <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -725,8 +700,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" s="5" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="C7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -741,14 +716,14 @@
       <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="C8" s="2" t="s">
         <v>26</v>
       </c>
@@ -766,7 +741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
@@ -776,10 +751,10 @@
       <c r="E9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -789,7 +764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="C10" s="2" t="s">
         <v>31</v>
       </c>
@@ -803,7 +778,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
@@ -816,7 +791,7 @@
       <c r="F11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -826,7 +801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="C12" s="2" t="s">
         <v>39</v>
       </c>
@@ -839,10 +814,10 @@
       <c r="F12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="8"/>
+      <c r="H12" s="4"/>
       <c r="I12" s="2" t="s">
         <v>14</v>
       </c>
@@ -850,7 +825,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="C13" s="2" t="s">
         <v>42</v>
       </c>
@@ -863,7 +838,7 @@
       <c r="F13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="1" t="s">
         <v>44</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -873,30 +848,30 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14">
-      <c r="C14" s="5" t="s">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="C14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="I14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
       <c r="C15" s="2" t="s">
         <v>50</v>
       </c>
@@ -916,7 +891,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="C16" s="2" t="s">
         <v>52</v>
       </c>
@@ -939,7 +914,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18">
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1">
       <c r="C18" s="2" t="s">
         <v>55</v>
       </c>
@@ -952,7 +928,7 @@
       <c r="F18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="1" t="s">
         <v>57</v>
       </c>
       <c r="I18" s="2" t="s">
@@ -962,7 +938,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20">
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1">
       <c r="C20" s="2" t="s">
         <v>58</v>
       </c>
@@ -985,7 +962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="C21" s="2" t="s">
         <v>63</v>
       </c>
@@ -1008,12 +985,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="C22" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24">
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="C24" s="2" t="s">
         <v>68</v>
       </c>
@@ -1026,7 +1004,7 @@
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="1" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="2" t="s">
@@ -1036,7 +1014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="C25" s="2" t="s">
         <v>72</v>
       </c>
@@ -1049,7 +1027,7 @@
       <c r="F25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="1" t="s">
         <v>75</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -1059,7 +1037,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="C26" s="2" t="s">
         <v>77</v>
       </c>
@@ -1072,7 +1050,7 @@
       <c r="F26" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="1" t="s">
         <v>80</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1082,7 +1060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="C27" s="2" t="s">
         <v>81</v>
       </c>
@@ -1095,7 +1073,7 @@
       <c r="F27" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="1" t="s">
         <v>84</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -1105,7 +1083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="C28" s="2" t="s">
         <v>85</v>
       </c>
@@ -1119,7 +1097,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="C29" s="2" t="s">
         <v>88</v>
       </c>
@@ -1132,39 +1110,107 @@
       <c r="F29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="7"/>
+      <c r="I29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="C30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="I30" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="J30" s="2" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B3"/>
@@ -1185,10 +1231,9 @@
     <hyperlink r:id="rId16" ref="G25"/>
     <hyperlink r:id="rId17" ref="G26"/>
     <hyperlink r:id="rId18" ref="G27"/>
-    <hyperlink r:id="rId19" ref="G29"/>
-    <hyperlink r:id="rId20" ref="G30"/>
+    <hyperlink r:id="rId19" ref="G30"/>
   </hyperlinks>
-  <drawing r:id="rId21"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -1197,8 +1242,112 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="11" width="12.57"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1"/>
+    <row r="2" ht="15.75" customHeight="1"/>
+    <row r="3" ht="15.75" customHeight="1"/>
+    <row r="4" ht="15.75" customHeight="1"/>
+    <row r="5" ht="15.75" customHeight="1"/>
+    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>